--- a/artfynd/A 11637-2025 artfynd.xlsx
+++ b/artfynd/A 11637-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120146766</v>
+        <v>120146767</v>
       </c>
       <c r="B2" t="n">
-        <v>105588</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>4660</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484089</v>
+        <v>484018</v>
       </c>
       <c r="R2" t="n">
-        <v>6544012</v>
+        <v>6544039</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,11 +748,6 @@
           <t>2024-08-30</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>medelålders</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -767,6 +757,16 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>torrträd av asp</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -779,6 +779,108 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120146766</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långstorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>484089</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6544012</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tångeråsa</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>medelålders</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
